--- a/DCA_prep-executions/DCA_Execution_SLATE_10-07-2026_v2.xlsx
+++ b/DCA_prep-executions/DCA_Execution_SLATE_10-07-2026_v2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alanl\Documents\GitHub\Stock_Picker\DCA_prep-executions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EA9D7FC1-F9A5-42F8-91DD-A1A98B8C3A96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9747818D-E5F3-478F-B353-F62292625224}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="21710" yWindow="630" windowWidth="16580" windowHeight="19590" xr2:uid="{81535BC7-C0A6-0A4F-99A4-E8B5751AB3B7}"/>
   </bookViews>
